--- a/exports/PATANJALI_full_report.xlsx
+++ b/exports/PATANJALI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>2.59</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>292</v>
+        <v>290.8</v>
       </c>
       <c r="I2" t="n">
         <v>291.800998634</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="L2" t="n">
         <v>0.8100000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>4.46</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>281.1</v>
+        <v>294.9</v>
       </c>
       <c r="I3" t="n">
         <v>285.0826614142636</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>3.34</v>
+        <v>-1.41</v>
       </c>
       <c r="L3" t="n">
-        <v>0.52</v>
+        <v>4.09</v>
       </c>
       <c r="M3" t="n">
         <v>2.1</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>275.3</v>
+        <v>262.3</v>
       </c>
       <c r="I4" t="n">
         <v>267.5460364626273</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.65</v>
+        <v>-11.05</v>
       </c>
       <c r="L4" t="n">
         <v>16.24</v>
@@ -669,7 +716,7 @@
         <v>2.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>-2.17</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.33</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>267.8</v>
+        <v>321.2</v>
       </c>
       <c r="I5" t="n">
         <v>288.8463672230514</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.1</v>
+        <v>-22.46</v>
       </c>
       <c r="L5" t="n">
-        <v>15.75</v>
+        <v>22.46</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9</v>
+        <v>10.49</v>
       </c>
       <c r="N5" t="n">
-        <v>6.81</v>
+        <v>19.94</v>
       </c>
       <c r="O5" t="n">
         <v>-8.140000000000001</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>17.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44637.55208333334</v>
+        <v>44641.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>333.3</v>
+        <v>305.7</v>
       </c>
       <c r="I6" t="n">
         <v>316.2629040646318</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.77</v>
+        <v>-4.83</v>
       </c>
       <c r="L6" t="n">
-        <v>10.99</v>
+        <v>13.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36</v>
+        <v>15.48</v>
       </c>
       <c r="N6" t="n">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>19.94</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>18.54</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44649.55208333334</v>
+        <v>44650.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>312.7</v>
+        <v>323.2</v>
       </c>
       <c r="I7" t="n">
         <v>315.8219540597131</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.29</v>
+        <v>-5.72</v>
       </c>
       <c r="L7" t="n">
-        <v>6.54</v>
+        <v>10.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17</v>
+        <v>3.39</v>
       </c>
       <c r="N7" t="n">
         <v>14.67</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>18.05</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44656.55208333334</v>
+        <v>44657.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>292.7</v>
+        <v>261</v>
       </c>
       <c r="I8" t="n">
         <v>266.2191259414222</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.44</v>
+        <v>-19.25</v>
       </c>
       <c r="L8" t="n">
-        <v>10.58</v>
+        <v>26.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.57</v>
+        <v>18.62</v>
       </c>
       <c r="N8" t="n">
-        <v>6.49</v>
+        <v>14.59</v>
       </c>
       <c r="O8" t="n">
         <v>4.03</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>20.34</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44659.55208333334</v>
+        <v>44662.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>312.3</v>
+        <v>325.1</v>
       </c>
       <c r="I9" t="n">
         <v>313.0562864450994</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>-19.66</v>
+        <v>-24.56</v>
       </c>
       <c r="L9" t="n">
-        <v>19.89</v>
+        <v>27.62</v>
       </c>
       <c r="M9" t="n">
         <v>3.9</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.15</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>346.8</v>
+        <v>335</v>
       </c>
       <c r="I10" t="n">
         <v>335.304488643344</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>6.67</v>
+        <v>3.05</v>
       </c>
       <c r="L10" t="n">
         <v>9.75</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>18.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44698.55208333334</v>
+        <v>44699.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>360.5</v>
+        <v>377.6</v>
       </c>
       <c r="I11" t="n">
         <v>365.5936408037998</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.61</v>
+        <v>-12.72</v>
       </c>
       <c r="L11" t="n">
-        <v>11.73</v>
+        <v>15.91</v>
       </c>
       <c r="M11" t="n">
         <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>9.94</v>
+        <v>10.24</v>
       </c>
       <c r="O11" t="n">
         <v>-9.140000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>15.64</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44705.55208333334</v>
+        <v>44706.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>366.4</v>
+        <v>348</v>
       </c>
       <c r="I12" t="n">
         <v>350.4695881862371</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.97</v>
+        <v>-7.84</v>
       </c>
       <c r="L12" t="n">
-        <v>3.95</v>
+        <v>7.84</v>
       </c>
       <c r="M12" t="n">
         <v>1.89</v>
       </c>
       <c r="N12" t="n">
-        <v>4.98</v>
+        <v>5.02</v>
       </c>
       <c r="O12" t="n">
         <v>10.24</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>16.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>351</v>
+        <v>357.3</v>
       </c>
       <c r="I13" t="n">
         <v>351.4657559438797</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.86</v>
+        <v>-2.67</v>
       </c>
       <c r="L13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.98</v>
+        <v>1.42</v>
       </c>
       <c r="N13" t="n">
         <v>5.03</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44831.55208333334</v>
+        <v>44832.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>450</v>
+        <v>449.3</v>
       </c>
       <c r="I14" t="n">
         <v>449.9730776176356</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>92.16666666666667</v>
+        <v>93</v>
       </c>
       <c r="K14" t="n">
-        <v>25.94</v>
+        <v>25.75</v>
       </c>
       <c r="L14" t="n">
         <v>6.61</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.15</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44897.55208333334</v>
+        <v>44900.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>426.4</v>
+        <v>432</v>
       </c>
       <c r="I15" t="n">
         <v>430.5388895861297</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>8.460000000000001</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.31</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>408.3</v>
+        <v>398.3</v>
       </c>
       <c r="I16" t="n">
         <v>403.9969422753616</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.49</v>
+        <v>-7.8</v>
       </c>
       <c r="L16" t="n">
-        <v>6.25</v>
+        <v>9.1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.54</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>392.3</v>
+        <v>397.9</v>
       </c>
       <c r="I17" t="n">
         <v>396.3785403697303</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>1.51</v>
+        <v>0.1</v>
       </c>
       <c r="L17" t="n">
         <v>2.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>386.7</v>
+        <v>368.1</v>
       </c>
       <c r="I18" t="n">
         <v>377.6855335190456</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.81</v>
+        <v>-7.49</v>
       </c>
       <c r="L18" t="n">
-        <v>5.76</v>
+        <v>7.49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.61</v>
+        <v>4.81</v>
       </c>
       <c r="N18" t="n">
-        <v>3.64</v>
+        <v>4.81</v>
       </c>
       <c r="O18" t="n">
         <v>1.12</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>320</v>
+        <v>328.4</v>
       </c>
       <c r="I19" t="n">
         <v>323.13897987073</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>13.07</v>
+        <v>10.79</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1524,7 +1751,7 @@
         <v>1.78</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>4.37</v>
       </c>
       <c r="O19" t="n">
         <v>-4.81</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.73</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>320</v>
+        <v>313.4</v>
       </c>
       <c r="I20" t="n">
         <v>313.53308415534</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.56</v>
+        <v>-4.57</v>
       </c>
       <c r="L20" t="n">
-        <v>6.27</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>0.37</v>
+        <v>4.06</v>
       </c>
       <c r="N20" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="O20" t="n">
         <v>4.37</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.94</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>308.6</v>
+        <v>323</v>
       </c>
       <c r="I21" t="n">
         <v>319.4837416727805</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>1.53</v>
+        <v>-3.06</v>
       </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>3.16</v>
       </c>
       <c r="M21" t="n">
         <v>0.71</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.15</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45119.55208333334</v>
+        <v>45120.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>408</v>
+        <v>388.4</v>
       </c>
       <c r="I22" t="n">
         <v>389.7850433979868</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>103.1666666666667</v>
+        <v>104</v>
       </c>
       <c r="K22" t="n">
-        <v>26.32</v>
+        <v>20.25</v>
       </c>
       <c r="L22" t="n">
         <v>7.34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
         <v>4.24</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.31</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45121.55208333334</v>
+        <v>45124.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>407.8</v>
+        <v>418.5</v>
       </c>
       <c r="I23" t="n">
         <v>410.4711148476306</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.99</v>
+        <v>-7.75</v>
       </c>
       <c r="L23" t="n">
-        <v>4.99</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>4.99</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>7.75</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>434</v>
+        <v>421.7</v>
       </c>
       <c r="I24" t="n">
         <v>429.9530446634066</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>0.76</v>
       </c>
       <c r="L24" t="n">
         <v>3.54</v>
       </c>
       <c r="M24" t="n">
-        <v>1.15</v>
+        <v>4.61</v>
       </c>
       <c r="N24" t="n">
         <v>2.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.06</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>430</v>
+        <v>435.1</v>
       </c>
       <c r="I25" t="n">
         <v>431.8770970438215</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.97</v>
+        <v>-3.18</v>
       </c>
       <c r="L25" t="n">
         <v>4.41</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.54</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>409.7</v>
+        <v>409</v>
       </c>
       <c r="I26" t="n">
         <v>409.3957023687854</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.84</v>
+        <v>-6</v>
       </c>
       <c r="L26" t="n">
-        <v>5.84</v>
+        <v>6.76</v>
       </c>
       <c r="M26" t="n">
         <v>1.53</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.44</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45208.55208333334</v>
+        <v>45209.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>412.1</v>
+        <v>433.7</v>
       </c>
       <c r="I27" t="n">
         <v>429.5570892986789</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.76</v>
+        <v>-6.04</v>
       </c>
       <c r="L27" t="n">
-        <v>2.91</v>
+        <v>6.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0.34</v>
+        <v>0.78</v>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>4.68</v>
       </c>
       <c r="O27" t="n">
         <v>-1.45</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.91</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>421.7</v>
+        <v>420.7</v>
       </c>
       <c r="I28" t="n">
         <v>421.6575710265611</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.77</v>
+        <v>-3</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.16</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>429</v>
+        <v>438.4</v>
       </c>
       <c r="I29" t="n">
         <v>435.7011665713907</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.97</v>
+        <v>-4.21</v>
       </c>
       <c r="L29" t="n">
-        <v>4.18</v>
+        <v>4.59</v>
       </c>
       <c r="M29" t="n">
         <v>0.38</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>456.9</v>
+        <v>447.7</v>
       </c>
       <c r="I30" t="n">
         <v>454.9122367457269</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>4.22</v>
+        <v>2.12</v>
       </c>
       <c r="L30" t="n">
         <v>2.51</v>
       </c>
       <c r="M30" t="n">
-        <v>0.15</v>
+        <v>0.79</v>
       </c>
       <c r="N30" t="n">
         <v>2.01</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.36</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>459.3</v>
+        <v>478</v>
       </c>
       <c r="I31" t="n">
         <v>471.7968600562951</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.59</v>
+        <v>-6.77</v>
       </c>
       <c r="L31" t="n">
-        <v>7.17</v>
+        <v>7.73</v>
       </c>
       <c r="M31" t="n">
         <v>2.48</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>523.3</v>
+        <v>515.5</v>
       </c>
       <c r="I32" t="n">
         <v>521.3394192713145</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K32" t="n">
-        <v>9.48</v>
+        <v>7.85</v>
       </c>
       <c r="L32" t="n">
         <v>3.68</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.49</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>535.8</v>
+        <v>545.3</v>
       </c>
       <c r="I33" t="n">
         <v>540.6629111531288</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.94</v>
+        <v>-5.78</v>
       </c>
       <c r="L33" t="n">
-        <v>4.66</v>
+        <v>7.14</v>
       </c>
       <c r="M33" t="n">
         <v>0.8100000000000001</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.91</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>526.2</v>
+        <v>516.7</v>
       </c>
       <c r="I34" t="n">
         <v>519.510168593189</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.5</v>
+        <v>-5.24</v>
       </c>
       <c r="L34" t="n">
-        <v>4.35</v>
+        <v>5.37</v>
       </c>
       <c r="M34" t="n">
         <v>3.67</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>9.49</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45338.55208333334</v>
+        <v>45341.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>544.7</v>
+        <v>560</v>
       </c>
       <c r="I35" t="n">
         <v>551.5208157184003</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.42</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>5.48</v>
+        <v>8.83</v>
       </c>
       <c r="M35" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
         <v>-3.06</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>539.3</v>
+        <v>514.4</v>
       </c>
       <c r="I36" t="n">
         <v>520.2496371037761</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.7</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>4.64</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M36" t="n">
         <v>2.75</v>
       </c>
       <c r="N36" t="n">
-        <v>1.26</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>2.26</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.24</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45401.55208333334</v>
+        <v>45404.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>468.5</v>
+        <v>483.3</v>
       </c>
       <c r="I37" t="n">
         <v>471.9309704559022</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K37" t="n">
-        <v>8.92</v>
+        <v>6.05</v>
       </c>
       <c r="L37" t="n">
         <v>6.34</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.09</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>487</v>
+        <v>477.4</v>
       </c>
       <c r="I38" t="n">
         <v>485.3335402374627</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>0.77</v>
+        <v>-1.22</v>
       </c>
       <c r="L38" t="n">
         <v>3.1</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.26</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>467.7</v>
+        <v>478.3</v>
       </c>
       <c r="I39" t="n">
         <v>477.5843218700269</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>2.03</v>
+        <v>-0.19</v>
       </c>
       <c r="L39" t="n">
         <v>2.49</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.69</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>489</v>
+        <v>429.3</v>
       </c>
       <c r="I40" t="n">
         <v>457.7883917749625</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>2.24</v>
+        <v>-10.24</v>
       </c>
       <c r="L40" t="n">
-        <v>2.76</v>
+        <v>18.46</v>
       </c>
       <c r="M40" t="n">
         <v>1.32</v>
       </c>
       <c r="N40" t="n">
-        <v>2.96</v>
+        <v>15.13</v>
       </c>
       <c r="O40" t="n">
         <v>2.27</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>16.53</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>465.5</v>
+        <v>493.1</v>
       </c>
       <c r="I41" t="n">
         <v>490.8986576324634</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.43</v>
+        <v>-14.86</v>
       </c>
       <c r="L41" t="n">
-        <v>13.44</v>
+        <v>17.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>8.06</v>
       </c>
       <c r="N41" t="n">
         <v>8.359999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.39</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45488.38541666666</v>
+        <v>45488.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>525.6</v>
+        <v>520.6</v>
       </c>
       <c r="I42" t="n">
         <v>521.0658408075369</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>6.59</v>
+        <v>5.58</v>
       </c>
       <c r="L42" t="n">
         <v>3.18</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>546.7</v>
+        <v>553.3</v>
       </c>
       <c r="I43" t="n">
         <v>549.7330629410707</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.01</v>
+        <v>-6.28</v>
       </c>
       <c r="L43" t="n">
-        <v>5.97</v>
+        <v>6.86</v>
       </c>
       <c r="M43" t="n">
         <v>0.51</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.93</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45548.38541666666</v>
+        <v>45548.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>623.3</v>
+        <v>619.6</v>
       </c>
       <c r="I44" t="n">
         <v>621.440933757877</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>12.65</v>
+        <v>11.98</v>
       </c>
       <c r="L44" t="n">
         <v>1.74</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.78</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45575.38541666666</v>
+        <v>45575.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>571.7</v>
+        <v>579.7</v>
       </c>
       <c r="I45" t="n">
         <v>571.770623167271</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>7.73</v>
+        <v>6.44</v>
       </c>
       <c r="L45" t="n">
         <v>0.84</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.53</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45590.38541666666</v>
+        <v>45590.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>567.3</v>
+        <v>546.3</v>
       </c>
       <c r="I46" t="n">
         <v>549.7423672672633</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.14</v>
+        <v>-5.76</v>
       </c>
       <c r="L46" t="n">
-        <v>2.79</v>
+        <v>5.81</v>
       </c>
       <c r="M46" t="n">
         <v>1.04</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>11.39</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45600.55208333334</v>
+        <v>45601.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>591.8</v>
+        <v>614</v>
       </c>
       <c r="I47" t="n">
         <v>608.5430642621651</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.33</v>
+        <v>-12.39</v>
       </c>
       <c r="L47" t="n">
-        <v>11.33</v>
+        <v>12.87</v>
       </c>
       <c r="M47" t="n">
-        <v>0.39</v>
+        <v>1.89</v>
       </c>
       <c r="N47" t="n">
         <v>7.21</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.52</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45617.38541666666</v>
+        <v>45617.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>594.3</v>
+        <v>585.7</v>
       </c>
       <c r="I48" t="n">
         <v>588.6742522699747</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.21</v>
+        <v>-4.61</v>
       </c>
       <c r="L48" t="n">
-        <v>4.33</v>
+        <v>5.91</v>
       </c>
       <c r="M48" t="n">
         <v>1.34</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.58</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45625.55208333334</v>
+        <v>45628.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>604.7</v>
+        <v>623</v>
       </c>
       <c r="I49" t="n">
         <v>612.8570272293476</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.24</v>
+        <v>-6.37</v>
       </c>
       <c r="L49" t="n">
-        <v>4.75</v>
+        <v>7.27</v>
       </c>
       <c r="M49" t="n">
         <v>1.69</v>
       </c>
       <c r="N49" t="n">
-        <v>2.49</v>
+        <v>2.79</v>
       </c>
       <c r="O49" t="n">
         <v>-4.72</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>7.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>599.7</v>
+        <v>588</v>
       </c>
       <c r="I50" t="n">
         <v>591.3676624975778</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.74</v>
+        <v>-5.62</v>
       </c>
       <c r="L50" t="n">
-        <v>5.23</v>
+        <v>6.13</v>
       </c>
       <c r="M50" t="n">
-        <v>0.57</v>
+        <v>2.48</v>
       </c>
       <c r="N50" t="n">
         <v>2.44</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.93</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45659.38541666666</v>
+        <v>45659.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>605.2</v>
+        <v>611.7</v>
       </c>
       <c r="I51" t="n">
         <v>609.199339339005</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.93</v>
+        <v>-4.03</v>
       </c>
       <c r="L51" t="n">
-        <v>4.03</v>
+        <v>5.22</v>
       </c>
       <c r="M51" t="n">
         <v>1.47</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.59</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>605.6</v>
+        <v>581.6</v>
       </c>
       <c r="I52" t="n">
         <v>583.4232480189968</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-1</v>
+        <v>-4.92</v>
       </c>
       <c r="L52" t="n">
-        <v>4.56</v>
+        <v>6.11</v>
       </c>
       <c r="M52" t="n">
         <v>0.15</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>11.16</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>601.1</v>
+        <v>618.4</v>
       </c>
       <c r="I53" t="n">
         <v>605.0270995552627</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.35</v>
+        <v>-6.33</v>
       </c>
       <c r="L53" t="n">
-        <v>7.75</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>1.7</v>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>4.14</v>
       </c>
       <c r="O53" t="n">
         <v>-0.76</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.72</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>616.5</v>
+        <v>585.2</v>
       </c>
       <c r="I54" t="n">
         <v>589.6623939706783</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.31</v>
+        <v>-5.37</v>
       </c>
       <c r="L54" t="n">
-        <v>2.12</v>
+        <v>6.13</v>
       </c>
       <c r="M54" t="n">
-        <v>0.42</v>
+        <v>2.4</v>
       </c>
       <c r="N54" t="n">
-        <v>1.52</v>
+        <v>3.91</v>
       </c>
       <c r="O54" t="n">
         <v>4.14</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.24</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>605.9</v>
+        <v>630.8</v>
       </c>
       <c r="I55" t="n">
         <v>627.2741583158379</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.54</v>
+        <v>-7.79</v>
       </c>
       <c r="L55" t="n">
-        <v>4.24</v>
+        <v>8.51</v>
       </c>
       <c r="M55" t="n">
         <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>3.98</v>
       </c>
       <c r="O55" t="n">
         <v>-3.91</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.71</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>633.8</v>
+        <v>627.7</v>
       </c>
       <c r="I56" t="n">
         <v>628.4470169728619</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="L56" t="n">
         <v>3.8</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.5</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>557.7</v>
+        <v>570.2</v>
       </c>
       <c r="I57" t="n">
         <v>558.2745516920443</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K57" t="n">
-        <v>11.15</v>
+        <v>9.16</v>
       </c>
       <c r="L57" t="n">
         <v>1.62</v>
@@ -3690,7 +4373,7 @@
         <v>1.36</v>
       </c>
       <c r="N57" t="n">
-        <v>2.24</v>
+        <v>3.94</v>
       </c>
       <c r="O57" t="n">
         <v>-1.81</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.03</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>624.3</v>
+        <v>613.5</v>
       </c>
       <c r="I58" t="n">
         <v>614.9264639781018</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>9.49</v>
+        <v>7.59</v>
       </c>
       <c r="L58" t="n">
         <v>2.26</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.14</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>602.65</v>
+        <v>604.9</v>
       </c>
       <c r="I59" t="n">
         <v>603.0691652166448</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>93</v>
+        <v>93.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="L59" t="n">
         <v>4.14</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.09</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>602.55</v>
+        <v>575.55</v>
       </c>
       <c r="I60" t="n">
         <v>586.1766270856098</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.39</v>
+        <v>-4.85</v>
       </c>
       <c r="L60" t="n">
-        <v>0.59</v>
+        <v>6.59</v>
       </c>
       <c r="M60" t="n">
         <v>-0</v>
       </c>
       <c r="N60" t="n">
-        <v>0.9</v>
+        <v>4.57</v>
       </c>
       <c r="O60" t="n">
         <v>2.08</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.72</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>551.15</v>
+        <v>558.4</v>
       </c>
       <c r="I61" t="n">
         <v>556.8199047630853</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K61" t="n">
-        <v>4.24</v>
+        <v>2.98</v>
       </c>
       <c r="L61" t="n">
         <v>5.46</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.26</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>551.8</v>
+        <v>550.45</v>
       </c>
       <c r="I62" t="n">
         <v>550.5434565451704</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.18</v>
+        <v>-1.42</v>
       </c>
       <c r="L62" t="n">
         <v>5.18</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.5</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>522.9</v>
+        <v>527.75</v>
       </c>
       <c r="I63" t="n">
         <v>526.9911367118067</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>5</v>
+        <v>4.12</v>
       </c>
       <c r="L63" t="n">
         <v>0.9399999999999999</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I64" t="n">
         <v>503.9210824622864</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.31</v>
+        <v>-5.26</v>
       </c>
       <c r="L64" t="n">
-        <v>4.93</v>
+        <v>6.01</v>
       </c>
       <c r="M64" t="n">
-        <v>0.26</v>
+        <v>0.99</v>
       </c>
       <c r="N64" t="n">
         <v>1.96</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.29</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>450</v>
+        <v>465.3</v>
       </c>
       <c r="I65" t="n">
         <v>464.4684896848253</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K65" t="n">
-        <v>10</v>
+        <v>6.94</v>
       </c>
       <c r="L65" t="n">
         <v>1.77</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.68</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>450</v>
+        <v>438.4</v>
       </c>
       <c r="I66" t="n">
         <v>445.9367075680636</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.29</v>
+        <v>-5.78</v>
       </c>
       <c r="L66" t="n">
-        <v>5.11</v>
+        <v>7.51</v>
       </c>
       <c r="M66" t="n">
         <v>0.22</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.27</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46280.55208333334</v>
+        <v>46281.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>338</v>
+        <v>354.45</v>
       </c>
       <c r="I67" t="n">
         <v>347.8143717141419</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>104.1666666666667</v>
+        <v>105</v>
       </c>
       <c r="K67" t="n">
-        <v>22.9</v>
+        <v>19.15</v>
       </c>
       <c r="L67" t="n">
         <v>3.05</v>
@@ -4260,7 +5063,7 @@
         <v>1.92</v>
       </c>
       <c r="N67" t="n">
-        <v>4.39</v>
+        <v>7.6</v>
       </c>
       <c r="O67" t="n">
         <v>-2.24</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.26</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>389.95</v>
+        <v>373.8</v>
       </c>
       <c r="I68" t="n">
         <v>381.7528078462971</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
-        <v>10.02</v>
+        <v>5.46</v>
       </c>
       <c r="L68" t="n">
         <v>4.78</v>
@@ -4317,7 +5132,7 @@
         <v>1.21</v>
       </c>
       <c r="N68" t="n">
-        <v>3.48</v>
+        <v>4.95</v>
       </c>
       <c r="O68" t="n">
         <v>7.6</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>38</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.3</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64.59999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.03</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.75</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.28</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.32</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.35</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.64</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.89</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7512,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.99</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.67</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
